--- a/senosiain/Ajuste Prog Vacaciones/Reporte de Actividades.xlsx
+++ b/senosiain/Ajuste Prog Vacaciones/Reporte de Actividades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Terceros\fortia\Senosiain\Ajuste Prog Vacaciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2DAB29-043F-4909-AC42-9A3FDE01DA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8381F4C1-0D21-4E56-9EB1-A07E942BC783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6476D554-FEC1-4C19-B81E-F48CB613D6B6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="53">
   <si>
     <t>Actividades</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>Los ajustes a objetos de base de datos se realizaron únicamente en el ambiente de desarrollo</t>
+  </si>
+  <si>
+    <t>Validación de ambiente de trabak</t>
   </si>
 </sst>
 </file>
@@ -421,7 +424,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -473,42 +476,67 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -517,35 +545,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1027,6 +1026,9 @@
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
   <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
     <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
       <we:customFunctionIdList>
         <we:customFunctionIds>_xldudf_AI_TABLE</we:customFunctionIds>
@@ -1055,6 +1057,9 @@
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
   <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
     <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
       <we:customFunctionIdList>
         <we:customFunctionIds>_xldudf_GPT</we:customFunctionIds>
@@ -1113,31 +1118,31 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="40" t="s">
+      <c r="C7" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="40" t="s">
+      <c r="E7" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="40" t="s">
+      <c r="F7" s="25" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="33" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="12"/>
-      <c r="C8" s="42">
+      <c r="C8" s="26">
         <v>46038</v>
       </c>
       <c r="D8" s="7">
@@ -1151,78 +1156,78 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="26"/>
-      <c r="B9" s="44" t="s">
+      <c r="A9" s="34"/>
+      <c r="B9" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="30"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="38"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
+      <c r="A10" s="34"/>
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="33"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="41"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="26"/>
+      <c r="A11" s="34"/>
       <c r="B11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="31"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="33"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="41"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="26"/>
+      <c r="A12" s="34"/>
       <c r="B12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="33"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="41"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
+      <c r="A13" s="34"/>
       <c r="B13" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="33"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="41"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="26"/>
+      <c r="A14" s="34"/>
       <c r="B14" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="33"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="41"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="27"/>
+      <c r="A15" s="35"/>
       <c r="B15" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="34"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="36"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="44"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="25" t="s">
-        <v>6</v>
+      <c r="A16" s="45" t="s">
+        <v>52</v>
       </c>
       <c r="B16" s="12"/>
       <c r="C16" s="6">
@@ -1239,147 +1244,147 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A17" s="26"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="30"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="38"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="26"/>
+      <c r="A18" s="34"/>
       <c r="B18" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="33"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="41"/>
     </row>
     <row r="19" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="26"/>
+      <c r="A19" s="34"/>
       <c r="B19" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="33"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="41"/>
     </row>
     <row r="20" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="26"/>
+      <c r="A20" s="34"/>
       <c r="B20" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="33"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="41"/>
     </row>
     <row r="21" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A21" s="26"/>
+      <c r="A21" s="34"/>
       <c r="B21" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="31"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="33"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="41"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="26"/>
+      <c r="A22" s="34"/>
       <c r="B22" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="31"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="33"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="41"/>
     </row>
     <row r="23" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="26"/>
+      <c r="A23" s="34"/>
       <c r="B23" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="31"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="33"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="41"/>
     </row>
     <row r="24" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A24" s="26"/>
+      <c r="A24" s="34"/>
       <c r="B24" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="31"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="33"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="41"/>
     </row>
     <row r="25" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A25" s="26"/>
+      <c r="A25" s="34"/>
       <c r="B25" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="33"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="41"/>
     </row>
     <row r="26" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A26" s="26"/>
+      <c r="A26" s="34"/>
       <c r="B26" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="33"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="41"/>
     </row>
     <row r="27" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A27" s="26"/>
+      <c r="A27" s="34"/>
       <c r="B27" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="31"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="33"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="41"/>
     </row>
     <row r="28" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A28" s="26"/>
+      <c r="A28" s="34"/>
       <c r="B28" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="31"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="33"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="41"/>
     </row>
     <row r="29" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A29" s="26"/>
+      <c r="A29" s="34"/>
       <c r="B29" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="31"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="33"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="41"/>
     </row>
     <row r="30" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A30" s="26"/>
+      <c r="A30" s="34"/>
       <c r="B30" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="31"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="33"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="41"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="47" t="s">
         <v>22</v>
       </c>
       <c r="B31" s="8"/>
@@ -1397,243 +1402,239 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="38"/>
+      <c r="A32" s="47"/>
       <c r="B32" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C32" s="37"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="37"/>
+      <c r="C32" s="46"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="38"/>
+      <c r="A33" s="47"/>
       <c r="B33" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="37"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="38"/>
+      <c r="A34" s="47"/>
       <c r="B34" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="38"/>
+      <c r="A35" s="47"/>
       <c r="B35" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="37"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="38"/>
+      <c r="A36" s="47"/>
       <c r="B36" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C36" s="37"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="37"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="38"/>
+      <c r="A37" s="47"/>
       <c r="B37" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="37"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="38"/>
+      <c r="A38" s="47"/>
       <c r="B38" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="37"/>
+      <c r="C38" s="46"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="38"/>
+      <c r="A39" s="47"/>
       <c r="B39" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C39" s="37"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="37"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="46"/>
+      <c r="F39" s="46"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="38"/>
+      <c r="A40" s="47"/>
       <c r="B40" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="37"/>
+      <c r="C40" s="46"/>
+      <c r="D40" s="46"/>
+      <c r="E40" s="46"/>
+      <c r="F40" s="46"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="38"/>
+      <c r="A41" s="47"/>
       <c r="B41" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
+      <c r="C41" s="46"/>
+      <c r="D41" s="46"/>
+      <c r="E41" s="46"/>
+      <c r="F41" s="46"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="38"/>
+      <c r="A42" s="47"/>
       <c r="B42" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="37"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="46"/>
+      <c r="F42" s="46"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="38"/>
+      <c r="A43" s="47"/>
       <c r="B43" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="37"/>
+      <c r="C43" s="46"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="46"/>
+      <c r="F43" s="46"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="38"/>
+      <c r="A44" s="47"/>
       <c r="B44" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="46"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="38"/>
+      <c r="A45" s="47"/>
       <c r="B45" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C45" s="37"/>
-      <c r="D45" s="37"/>
-      <c r="E45" s="37"/>
-      <c r="F45" s="37"/>
+      <c r="C45" s="46"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="46"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="38"/>
+      <c r="A46" s="47"/>
       <c r="B46" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C46" s="37"/>
-      <c r="D46" s="37"/>
-      <c r="E46" s="37"/>
-      <c r="F46" s="37"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="46"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="38"/>
+      <c r="A47" s="47"/>
       <c r="B47" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C47" s="37"/>
-      <c r="D47" s="37"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="37"/>
+      <c r="C47" s="46"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="46"/>
     </row>
     <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B48" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C48" s="39">
+      <c r="C48" s="48">
         <f>+F31+F16+F8</f>
         <v>17</v>
       </c>
-      <c r="D48" s="39"/>
-      <c r="E48" s="39"/>
-      <c r="F48" s="39"/>
-    </row>
-    <row r="52" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="46" t="s">
+      <c r="D48" s="48"/>
+      <c r="E48" s="48"/>
+      <c r="F48" s="48"/>
+    </row>
+    <row r="52" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="29" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="B53" s="50"/>
-      <c r="C53" s="45"/>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="49"/>
-      <c r="B54" s="49"/>
-    </row>
-    <row r="55" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="46" t="s">
+      <c r="B53" s="32"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="31"/>
+      <c r="B54" s="31"/>
+    </row>
+    <row r="55" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="29" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="50" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="B56" s="45"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="50" t="s">
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B57" s="45"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="50" t="s">
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="B58" s="45"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="47"/>
-    </row>
-    <row r="60" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="46" t="s">
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="30"/>
+    </row>
+    <row r="60" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="29" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="48" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="31" t="s">
         <v>51</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="C48:F48"/>
     <mergeCell ref="A8:A15"/>
     <mergeCell ref="C9:F15"/>
     <mergeCell ref="A16:A30"/>
     <mergeCell ref="C17:F30"/>
     <mergeCell ref="C32:F47"/>
     <mergeCell ref="A31:A47"/>
-    <mergeCell ref="C48:F48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
